--- a/iLgs/App_Data/CustodianLandAnnexTemplate.xlsx
+++ b/iLgs/App_Data/CustodianLandAnnexTemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Templates New/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{7CC42C42-5EF6-44D1-BB1B-1CA673CDEFC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9E07CEB-B0D9-43C4-8D7F-A50AF43E9C53}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{7CC42C42-5EF6-44D1-BB1B-1CA673CDEFC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1061E8B-9EEA-4D7A-9956-A30055ADEAAE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{936140C4-A9C3-41AD-97AE-F1FBAF5E2091}"/>
   </bookViews>
@@ -601,7 +601,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -624,117 +624,10 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
@@ -750,11 +643,119 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1075,7 +1076,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A0BCCD5-0F1C-4D2A-A2F8-C15AA1846C99}">
-  <dimension ref="A2:Z15"/>
+  <dimension ref="A2:Z16"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="18.5546875" style="1" customWidth="1"/>
@@ -1107,263 +1108,268 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:26" ht="17.399999999999999">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="11" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:26">
       <c r="A3" s="5"/>
     </row>
-    <row r="4" spans="1:26" ht="15.6">
-      <c r="A4" s="7" t="s">
+    <row r="4" spans="1:26">
+      <c r="A4" s="5"/>
+    </row>
+    <row r="5" spans="1:26" ht="15.6">
+      <c r="A5" s="7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="16.2" thickBot="1">
-      <c r="A5" s="7"/>
-    </row>
-    <row r="6" spans="1:26" ht="15.6" thickTop="1" thickBot="1">
-      <c r="A6" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="30" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="38" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" s="51" t="s">
-        <v>5</v>
-      </c>
-      <c r="G6" s="52" t="s">
-        <v>6</v>
-      </c>
-      <c r="H6" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="I6" s="42" t="s">
-        <v>8</v>
-      </c>
-      <c r="J6" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="K6" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="L6" s="42" t="s">
-        <v>11</v>
-      </c>
-      <c r="M6" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="N6" s="35" t="s">
-        <v>13</v>
-      </c>
-      <c r="O6" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="P6" s="30" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q6" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="R6" s="47"/>
-      <c r="S6" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="T6" s="12"/>
-      <c r="U6" s="40" t="s">
-        <v>18</v>
-      </c>
-      <c r="V6" s="40"/>
-      <c r="W6" s="40"/>
-      <c r="X6" s="41"/>
-      <c r="Y6" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z6" s="14" t="s">
-        <v>20</v>
-      </c>
+    <row r="6" spans="1:26" ht="16.2" thickBot="1">
+      <c r="A6" s="7"/>
     </row>
     <row r="7" spans="1:26" ht="15.6" thickTop="1" thickBot="1">
-      <c r="A7" s="28"/>
-      <c r="B7" s="31"/>
-      <c r="C7" s="33"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="33"/>
-      <c r="I7" s="43"/>
-      <c r="J7" s="43"/>
-      <c r="K7" s="43"/>
-      <c r="L7" s="43"/>
-      <c r="M7" s="45"/>
-      <c r="N7" s="45"/>
-      <c r="O7" s="33"/>
-      <c r="P7" s="33"/>
-      <c r="Q7" s="17" t="s">
+      <c r="A7" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="36" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="H7" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="I7" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="J7" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="K7" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="L7" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="M7" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="N7" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="O7" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="P7" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q7" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="R7" s="32"/>
+      <c r="S7" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="T7" s="38"/>
+      <c r="U7" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="V7" s="53"/>
+      <c r="W7" s="53"/>
+      <c r="X7" s="54"/>
+      <c r="Y7" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z7" s="40" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" ht="15.6" thickTop="1" thickBot="1">
+      <c r="A8" s="17"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="23"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="29"/>
+      <c r="N8" s="29"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="23"/>
+      <c r="Q8" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="R7" s="19" t="s">
+      <c r="R8" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="S7" s="21" t="s">
+      <c r="S8" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="T7" s="23" t="s">
+      <c r="T8" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="U7" s="25" t="s">
+      <c r="U8" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="V7" s="25"/>
-      <c r="W7" s="25" t="s">
+      <c r="V8" s="51"/>
+      <c r="W8" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="X7" s="26"/>
-      <c r="Y7" s="13"/>
-      <c r="Z7" s="15"/>
+      <c r="X8" s="52"/>
+      <c r="Y8" s="39"/>
+      <c r="Z8" s="41"/>
     </row>
-    <row r="8" spans="1:26" ht="44.4" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A8" s="29"/>
-      <c r="B8" s="32"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="34"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="44"/>
-      <c r="K8" s="44"/>
-      <c r="L8" s="44"/>
-      <c r="M8" s="46"/>
-      <c r="N8" s="46"/>
-      <c r="O8" s="34"/>
-      <c r="P8" s="34"/>
-      <c r="Q8" s="18"/>
-      <c r="R8" s="20"/>
-      <c r="S8" s="22"/>
-      <c r="T8" s="24"/>
-      <c r="U8" s="2" t="s">
+    <row r="9" spans="1:26" ht="44.4" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A9" s="18"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="27"/>
+      <c r="K9" s="27"/>
+      <c r="L9" s="27"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="30"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="44"/>
+      <c r="R9" s="46"/>
+      <c r="S9" s="48"/>
+      <c r="T9" s="50"/>
+      <c r="U9" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="V8" s="3" t="s">
+      <c r="V9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="W8" s="2" t="s">
+      <c r="W9" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="X8" s="4" t="s">
+      <c r="X9" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="Y8" s="13"/>
-      <c r="Z8" s="16"/>
+      <c r="Y9" s="39"/>
+      <c r="Z9" s="42"/>
     </row>
-    <row r="9" spans="1:26" ht="15" thickTop="1"/>
-    <row r="11" spans="1:26">
-      <c r="A11" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9" t="s">
-        <v>34</v>
-      </c>
+    <row r="10" spans="1:26" ht="15" thickTop="1">
+      <c r="N10" s="12"/>
     </row>
     <row r="12" spans="1:26">
-      <c r="A12" s="8"/>
+      <c r="A12" s="8" t="s">
+        <v>30</v>
+      </c>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
+      <c r="G12" s="9" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="13" spans="1:26">
-      <c r="A13" s="9"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
       <c r="F13" s="9"/>
       <c r="G13" s="9"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
     </row>
     <row r="14" spans="1:26">
       <c r="A14" s="9"/>
-      <c r="B14" s="50" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="50"/>
-      <c r="D14" s="50"/>
-      <c r="E14" s="50"/>
-      <c r="H14" s="48" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="48"/>
-      <c r="J14" s="48"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
     </row>
     <row r="15" spans="1:26">
       <c r="A15" s="9"/>
-      <c r="B15" s="49" t="s">
+      <c r="B15" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="H15" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
+    </row>
+    <row r="16" spans="1:26">
+      <c r="A16" s="9"/>
+      <c r="B16" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="49"/>
-      <c r="D15" s="49"/>
-      <c r="E15" s="49"/>
-      <c r="H15" s="49" t="s">
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="H16" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="I15" s="49"/>
-      <c r="J15" s="49"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="Y7:Y9"/>
+    <mergeCell ref="Z7:Z9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:V8"/>
+    <mergeCell ref="W8:X8"/>
+    <mergeCell ref="U7:X7"/>
+    <mergeCell ref="K7:K9"/>
+    <mergeCell ref="L7:L9"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="O7:O9"/>
+    <mergeCell ref="P7:P9"/>
+    <mergeCell ref="Q7:R7"/>
     <mergeCell ref="H15:J15"/>
-    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="H16:J16"/>
     <mergeCell ref="B15:E15"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="G6:G8"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="O6:O8"/>
-    <mergeCell ref="P6:P8"/>
-    <mergeCell ref="Q6:R6"/>
-    <mergeCell ref="H6:H8"/>
-    <mergeCell ref="I6:I8"/>
-    <mergeCell ref="J6:J8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="L6:L8"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="Y6:Y8"/>
-    <mergeCell ref="Z6:Z8"/>
-    <mergeCell ref="Q7:Q8"/>
-    <mergeCell ref="R7:R8"/>
-    <mergeCell ref="S7:S8"/>
-    <mergeCell ref="T7:T8"/>
-    <mergeCell ref="U7:V7"/>
-    <mergeCell ref="W7:X7"/>
-    <mergeCell ref="U6:X6"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="F7:F9"/>
+    <mergeCell ref="G7:G9"/>
+    <mergeCell ref="H7:H9"/>
+    <mergeCell ref="I7:I9"/>
+    <mergeCell ref="J7:J9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/iLgs/App_Data/CustodianLandAnnexTemplate.xlsx
+++ b/iLgs/App_Data/CustodianLandAnnexTemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Templates New/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{7CC42C42-5EF6-44D1-BB1B-1CA673CDEFC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1061E8B-9EEA-4D7A-9956-A30055ADEAAE}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="8_{7CC42C42-5EF6-44D1-BB1B-1CA673CDEFC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD15558D-CCE8-4B11-A3FE-82D013676BDE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{936140C4-A9C3-41AD-97AE-F1FBAF5E2091}"/>
   </bookViews>
@@ -601,7 +601,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -627,7 +627,117 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
@@ -643,119 +753,14 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1130,133 +1135,133 @@
       <c r="A7" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="28" t="s">
+      <c r="D7" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="36" t="s">
+      <c r="E7" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="22" t="s">
+      <c r="H7" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="25" t="s">
+      <c r="I7" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="25" t="s">
+      <c r="J7" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="25" t="s">
+      <c r="K7" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="25" t="s">
+      <c r="L7" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="28" t="s">
+      <c r="M7" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="28" t="s">
+      <c r="N7" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="O7" s="22" t="s">
+      <c r="O7" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="P7" s="22" t="s">
+      <c r="P7" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="Q7" s="31" t="s">
+      <c r="Q7" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="R7" s="32"/>
-      <c r="S7" s="31" t="s">
+      <c r="R7" s="48"/>
+      <c r="S7" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="T7" s="38"/>
-      <c r="U7" s="53" t="s">
+      <c r="T7" s="13"/>
+      <c r="U7" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="V7" s="53"/>
-      <c r="W7" s="53"/>
-      <c r="X7" s="54"/>
-      <c r="Y7" s="39" t="s">
+      <c r="V7" s="28"/>
+      <c r="W7" s="28"/>
+      <c r="X7" s="29"/>
+      <c r="Y7" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="Z7" s="40" t="s">
+      <c r="Z7" s="15" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="15.6" thickTop="1" thickBot="1">
-      <c r="A8" s="17"/>
-      <c r="B8" s="20"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="26"/>
-      <c r="K8" s="26"/>
-      <c r="L8" s="26"/>
-      <c r="M8" s="29"/>
-      <c r="N8" s="29"/>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="43" t="s">
+      <c r="A8" s="34"/>
+      <c r="B8" s="37"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="31"/>
+      <c r="M8" s="46"/>
+      <c r="N8" s="46"/>
+      <c r="O8" s="39"/>
+      <c r="P8" s="39"/>
+      <c r="Q8" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="R8" s="45" t="s">
+      <c r="R8" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="S8" s="47" t="s">
+      <c r="S8" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="T8" s="49" t="s">
+      <c r="T8" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="U8" s="51" t="s">
+      <c r="U8" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="V8" s="51"/>
-      <c r="W8" s="51" t="s">
+      <c r="V8" s="26"/>
+      <c r="W8" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="X8" s="52"/>
-      <c r="Y8" s="39"/>
-      <c r="Z8" s="41"/>
+      <c r="X8" s="27"/>
+      <c r="Y8" s="14"/>
+      <c r="Z8" s="16"/>
     </row>
     <row r="9" spans="1:26" ht="44.4" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A9" s="18"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="24"/>
-      <c r="I9" s="27"/>
-      <c r="J9" s="27"/>
-      <c r="K9" s="27"/>
-      <c r="L9" s="27"/>
-      <c r="M9" s="30"/>
-      <c r="N9" s="30"/>
-      <c r="O9" s="24"/>
-      <c r="P9" s="24"/>
-      <c r="Q9" s="44"/>
-      <c r="R9" s="46"/>
-      <c r="S9" s="48"/>
-      <c r="T9" s="50"/>
+      <c r="A9" s="35"/>
+      <c r="B9" s="38"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="32"/>
+      <c r="K9" s="32"/>
+      <c r="L9" s="32"/>
+      <c r="M9" s="47"/>
+      <c r="N9" s="47"/>
+      <c r="O9" s="40"/>
+      <c r="P9" s="40"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="21"/>
+      <c r="S9" s="23"/>
+      <c r="T9" s="25"/>
       <c r="U9" s="2" t="s">
         <v>27</v>
       </c>
@@ -1269,11 +1274,64 @@
       <c r="X9" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="Y9" s="39"/>
-      <c r="Z9" s="42"/>
+      <c r="Y9" s="14"/>
+      <c r="Z9" s="17"/>
     </row>
     <row r="10" spans="1:26" ht="15" thickTop="1">
-      <c r="N10" s="12"/>
+      <c r="A10" s="54"/>
+      <c r="B10" s="54"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="54"/>
+      <c r="K10" s="54"/>
+      <c r="L10" s="54"/>
+      <c r="M10" s="54"/>
+      <c r="N10" s="55"/>
+      <c r="O10" s="54"/>
+      <c r="P10" s="54"/>
+      <c r="Q10" s="54"/>
+      <c r="R10" s="54"/>
+      <c r="S10" s="54"/>
+      <c r="T10" s="54"/>
+      <c r="U10" s="54"/>
+      <c r="V10" s="54"/>
+      <c r="W10" s="54"/>
+      <c r="X10" s="54"/>
+      <c r="Y10" s="54"/>
+      <c r="Z10" s="54"/>
+    </row>
+    <row r="11" spans="1:26">
+      <c r="A11" s="54"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="54"/>
+      <c r="K11" s="54"/>
+      <c r="L11" s="54"/>
+      <c r="M11" s="54"/>
+      <c r="N11" s="54"/>
+      <c r="O11" s="54"/>
+      <c r="P11" s="54"/>
+      <c r="Q11" s="54"/>
+      <c r="R11" s="54"/>
+      <c r="S11" s="54"/>
+      <c r="T11" s="54"/>
+      <c r="U11" s="54"/>
+      <c r="V11" s="54"/>
+      <c r="W11" s="54"/>
+      <c r="X11" s="54"/>
+      <c r="Y11" s="54"/>
+      <c r="Z11" s="54"/>
     </row>
     <row r="12" spans="1:26">
       <c r="A12" s="8" t="s">
@@ -1311,34 +1369,55 @@
     </row>
     <row r="15" spans="1:26">
       <c r="A15" s="9"/>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="H15" s="13" t="s">
+      <c r="C15" s="51"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51"/>
+      <c r="H15" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
+      <c r="I15" s="49"/>
+      <c r="J15" s="49"/>
     </row>
     <row r="16" spans="1:26">
       <c r="A16" s="9"/>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="H16" s="14" t="s">
+      <c r="C16" s="50"/>
+      <c r="D16" s="50"/>
+      <c r="E16" s="50"/>
+      <c r="H16" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14"/>
+      <c r="I16" s="50"/>
+      <c r="J16" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="H15:J15"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="F7:F9"/>
+    <mergeCell ref="G7:G9"/>
+    <mergeCell ref="H7:H9"/>
+    <mergeCell ref="I7:I9"/>
+    <mergeCell ref="J7:J9"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="O7:O9"/>
+    <mergeCell ref="P7:P9"/>
+    <mergeCell ref="Q7:R7"/>
+    <mergeCell ref="K7:K9"/>
+    <mergeCell ref="L7:L9"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="E7:E9"/>
     <mergeCell ref="S7:T7"/>
     <mergeCell ref="Y7:Y9"/>
     <mergeCell ref="Z7:Z9"/>
@@ -1349,27 +1428,6 @@
     <mergeCell ref="U8:V8"/>
     <mergeCell ref="W8:X8"/>
     <mergeCell ref="U7:X7"/>
-    <mergeCell ref="K7:K9"/>
-    <mergeCell ref="L7:L9"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="M7:M9"/>
-    <mergeCell ref="N7:N9"/>
-    <mergeCell ref="O7:O9"/>
-    <mergeCell ref="P7:P9"/>
-    <mergeCell ref="Q7:R7"/>
-    <mergeCell ref="H15:J15"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="F7:F9"/>
-    <mergeCell ref="G7:G9"/>
-    <mergeCell ref="H7:H9"/>
-    <mergeCell ref="I7:I9"/>
-    <mergeCell ref="J7:J9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/iLgs/App_Data/CustodianLandAnnexTemplate.xlsx
+++ b/iLgs/App_Data/CustodianLandAnnexTemplate.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Templates New/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="8_{7CC42C42-5EF6-44D1-BB1B-1CA673CDEFC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD15558D-CCE8-4B11-A3FE-82D013676BDE}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="8_{7CC42C42-5EF6-44D1-BB1B-1CA673CDEFC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7D83539-B5CF-4B88-9C0F-96A9DADE0E43}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{936140C4-A9C3-41AD-97AE-F1FBAF5E2091}"/>
   </bookViews>
@@ -229,7 +229,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -594,6 +594,15 @@
         <color indexed="64"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -601,7 +610,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -627,116 +636,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
@@ -753,14 +654,134 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="1" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -778,10 +799,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1081,7 +1098,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A0BCCD5-0F1C-4D2A-A2F8-C15AA1846C99}">
-  <dimension ref="A2:Z16"/>
+  <dimension ref="A2:Z17"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="18.5546875" style="1" customWidth="1"/>
@@ -1135,133 +1152,133 @@
       <c r="A7" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="41" t="s">
+      <c r="D7" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="44" t="s">
+      <c r="E7" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="52" t="s">
+      <c r="F7" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="53" t="s">
+      <c r="G7" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="36" t="s">
+      <c r="H7" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="30" t="s">
+      <c r="I7" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="30" t="s">
+      <c r="J7" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="30" t="s">
+      <c r="K7" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="30" t="s">
+      <c r="L7" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="41" t="s">
+      <c r="M7" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="41" t="s">
+      <c r="N7" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="O7" s="36" t="s">
+      <c r="O7" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="P7" s="36" t="s">
+      <c r="P7" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="Q7" s="12" t="s">
+      <c r="Q7" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="R7" s="48"/>
-      <c r="S7" s="12" t="s">
+      <c r="R7" s="32"/>
+      <c r="S7" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="T7" s="13"/>
-      <c r="U7" s="28" t="s">
+      <c r="T7" s="38"/>
+      <c r="U7" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="V7" s="28"/>
-      <c r="W7" s="28"/>
-      <c r="X7" s="29"/>
-      <c r="Y7" s="14" t="s">
+      <c r="V7" s="53"/>
+      <c r="W7" s="53"/>
+      <c r="X7" s="54"/>
+      <c r="Y7" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="Z7" s="15" t="s">
+      <c r="Z7" s="40" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="15.6" thickTop="1" thickBot="1">
-      <c r="A8" s="34"/>
-      <c r="B8" s="37"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="31"/>
-      <c r="J8" s="31"/>
-      <c r="K8" s="31"/>
-      <c r="L8" s="31"/>
-      <c r="M8" s="46"/>
-      <c r="N8" s="46"/>
-      <c r="O8" s="39"/>
-      <c r="P8" s="39"/>
-      <c r="Q8" s="18" t="s">
+      <c r="A8" s="17"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="23"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="29"/>
+      <c r="N8" s="29"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="23"/>
+      <c r="Q8" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="R8" s="20" t="s">
+      <c r="R8" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="S8" s="22" t="s">
+      <c r="S8" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="T8" s="24" t="s">
+      <c r="T8" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="U8" s="26" t="s">
+      <c r="U8" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="V8" s="26"/>
-      <c r="W8" s="26" t="s">
+      <c r="V8" s="51"/>
+      <c r="W8" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="X8" s="27"/>
-      <c r="Y8" s="14"/>
-      <c r="Z8" s="16"/>
+      <c r="X8" s="52"/>
+      <c r="Y8" s="39"/>
+      <c r="Z8" s="41"/>
     </row>
     <row r="9" spans="1:26" ht="44.4" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A9" s="35"/>
-      <c r="B9" s="38"/>
-      <c r="C9" s="40"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="45"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="40"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
-      <c r="K9" s="32"/>
-      <c r="L9" s="32"/>
-      <c r="M9" s="47"/>
-      <c r="N9" s="47"/>
-      <c r="O9" s="40"/>
-      <c r="P9" s="40"/>
-      <c r="Q9" s="19"/>
-      <c r="R9" s="21"/>
-      <c r="S9" s="23"/>
-      <c r="T9" s="25"/>
+      <c r="A9" s="18"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="27"/>
+      <c r="K9" s="27"/>
+      <c r="L9" s="27"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="30"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="44"/>
+      <c r="R9" s="46"/>
+      <c r="S9" s="48"/>
+      <c r="T9" s="50"/>
       <c r="U9" s="2" t="s">
         <v>27</v>
       </c>
@@ -1274,150 +1291,157 @@
       <c r="X9" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="Y9" s="14"/>
-      <c r="Z9" s="17"/>
-    </row>
-    <row r="10" spans="1:26" ht="15" thickTop="1">
-      <c r="A10" s="54"/>
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="54"/>
-      <c r="J10" s="54"/>
-      <c r="K10" s="54"/>
-      <c r="L10" s="54"/>
-      <c r="M10" s="54"/>
-      <c r="N10" s="55"/>
-      <c r="O10" s="54"/>
-      <c r="P10" s="54"/>
-      <c r="Q10" s="54"/>
-      <c r="R10" s="54"/>
-      <c r="S10" s="54"/>
-      <c r="T10" s="54"/>
-      <c r="U10" s="54"/>
-      <c r="V10" s="54"/>
-      <c r="W10" s="54"/>
-      <c r="X10" s="54"/>
-      <c r="Y10" s="54"/>
-      <c r="Z10" s="54"/>
+      <c r="Y9" s="39"/>
+      <c r="Z9" s="42"/>
+    </row>
+    <row r="10" spans="1:26" ht="0.6" customHeight="1" thickTop="1">
+      <c r="A10" s="57"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="58"/>
+      <c r="I10" s="59"/>
+      <c r="J10" s="59"/>
+      <c r="K10" s="59"/>
+      <c r="L10" s="59"/>
+      <c r="M10" s="58"/>
+      <c r="N10" s="58"/>
+      <c r="O10" s="58"/>
+      <c r="P10" s="58"/>
+      <c r="Q10" s="58"/>
+      <c r="R10" s="58"/>
+      <c r="S10" s="57"/>
+      <c r="T10" s="57"/>
+      <c r="U10" s="57"/>
+      <c r="V10" s="58"/>
+      <c r="W10" s="57"/>
+      <c r="X10" s="58"/>
+      <c r="Y10" s="57"/>
+      <c r="Z10" s="57"/>
     </row>
     <row r="11" spans="1:26">
-      <c r="A11" s="54"/>
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="54"/>
-      <c r="J11" s="54"/>
-      <c r="K11" s="54"/>
-      <c r="L11" s="54"/>
-      <c r="M11" s="54"/>
-      <c r="N11" s="54"/>
-      <c r="O11" s="54"/>
-      <c r="P11" s="54"/>
-      <c r="Q11" s="54"/>
-      <c r="R11" s="54"/>
-      <c r="S11" s="54"/>
-      <c r="T11" s="54"/>
-      <c r="U11" s="54"/>
-      <c r="V11" s="54"/>
-      <c r="W11" s="54"/>
-      <c r="X11" s="54"/>
-      <c r="Y11" s="54"/>
-      <c r="Z11" s="54"/>
+      <c r="A11" s="55"/>
+      <c r="B11" s="55"/>
+      <c r="C11" s="55"/>
+      <c r="D11" s="55"/>
+      <c r="E11" s="55"/>
+      <c r="F11" s="55"/>
+      <c r="G11" s="55"/>
+      <c r="H11" s="55"/>
+      <c r="I11" s="55"/>
+      <c r="J11" s="55"/>
+      <c r="K11" s="55"/>
+      <c r="L11" s="55"/>
+      <c r="M11" s="55"/>
+      <c r="N11" s="56"/>
+      <c r="O11" s="55"/>
+      <c r="P11" s="55"/>
+      <c r="Q11" s="55"/>
+      <c r="R11" s="55"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="55"/>
+      <c r="U11" s="55"/>
+      <c r="V11" s="55"/>
+      <c r="W11" s="55"/>
+      <c r="X11" s="55"/>
+      <c r="Y11" s="55"/>
+      <c r="Z11" s="55"/>
     </row>
     <row r="12" spans="1:26">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="12"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="12"/>
+      <c r="P12" s="12"/>
+      <c r="Q12" s="12"/>
+      <c r="R12" s="12"/>
+      <c r="S12" s="12"/>
+      <c r="T12" s="12"/>
+      <c r="U12" s="12"/>
+      <c r="V12" s="12"/>
+      <c r="W12" s="12"/>
+      <c r="X12" s="12"/>
+      <c r="Y12" s="12"/>
+      <c r="Z12" s="12"/>
+    </row>
+    <row r="13" spans="1:26">
+      <c r="A13" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26">
-      <c r="A13" s="8"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
+      <c r="G13" s="9" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="14" spans="1:26">
-      <c r="A14" s="9"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
     </row>
     <row r="15" spans="1:26">
       <c r="A15" s="9"/>
-      <c r="B15" s="51" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="51"/>
-      <c r="D15" s="51"/>
-      <c r="E15" s="51"/>
-      <c r="H15" s="49" t="s">
-        <v>31</v>
-      </c>
-      <c r="I15" s="49"/>
-      <c r="J15" s="49"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
     </row>
     <row r="16" spans="1:26">
       <c r="A16" s="9"/>
-      <c r="B16" s="50" t="s">
+      <c r="B16" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="H16" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="13"/>
+      <c r="J16" s="13"/>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="9"/>
+      <c r="B17" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="50"/>
-      <c r="D16" s="50"/>
-      <c r="E16" s="50"/>
-      <c r="H16" s="50" t="s">
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="H17" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="I16" s="50"/>
-      <c r="J16" s="50"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="H15:J15"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="F7:F9"/>
-    <mergeCell ref="G7:G9"/>
-    <mergeCell ref="H7:H9"/>
-    <mergeCell ref="I7:I9"/>
-    <mergeCell ref="J7:J9"/>
-    <mergeCell ref="M7:M9"/>
-    <mergeCell ref="N7:N9"/>
-    <mergeCell ref="O7:O9"/>
-    <mergeCell ref="P7:P9"/>
-    <mergeCell ref="Q7:R7"/>
-    <mergeCell ref="K7:K9"/>
-    <mergeCell ref="L7:L9"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="E7:E9"/>
     <mergeCell ref="S7:T7"/>
     <mergeCell ref="Y7:Y9"/>
     <mergeCell ref="Z7:Z9"/>
@@ -1428,6 +1452,27 @@
     <mergeCell ref="U8:V8"/>
     <mergeCell ref="W8:X8"/>
     <mergeCell ref="U7:X7"/>
+    <mergeCell ref="K7:K9"/>
+    <mergeCell ref="L7:L9"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="O7:O9"/>
+    <mergeCell ref="P7:P9"/>
+    <mergeCell ref="Q7:R7"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="F7:F9"/>
+    <mergeCell ref="G7:G9"/>
+    <mergeCell ref="H7:H9"/>
+    <mergeCell ref="I7:I9"/>
+    <mergeCell ref="J7:J9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/iLgs/App_Data/CustodianLandAnnexTemplate.xlsx
+++ b/iLgs/App_Data/CustodianLandAnnexTemplate.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Template  2025_04_22/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Tempalte 2025_06_24/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{4CCB3B42-D639-4A82-BB32-781160A643F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80CCC4D2-7CA9-4D94-8AD2-3058F0A71694}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{4CCB3B42-D639-4A82-BB32-781160A643F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D55BD21-FA9E-4693-9B09-169A9731D6B4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" tabRatio="986" xr2:uid="{8F9EB15D-4C1E-42CC-8141-A131BDAE685A}"/>
   </bookViews>
@@ -658,7 +658,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -673,9 +673,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -706,9 +703,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -718,16 +712,40 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -736,43 +754,65 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="7" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="7" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="7" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="7" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -791,10 +831,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1098,352 +1134,466 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="20.77734375" style="9" customWidth="1"/>
-    <col min="3" max="3" width="8" style="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="8"/>
-    <col min="6" max="6" width="8.109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.77734375" style="19" customWidth="1"/>
-    <col min="8" max="8" width="11.6640625" style="19" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" style="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.77734375" style="19" customWidth="1"/>
-    <col min="11" max="11" width="9.88671875" style="19" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.77734375" style="8" customWidth="1"/>
-    <col min="14" max="14" width="12.88671875" style="9" customWidth="1"/>
-    <col min="15" max="15" width="17.5546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.5546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.77734375" style="9" customWidth="1"/>
-    <col min="19" max="19" width="14.109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="15.109375" style="19" customWidth="1"/>
-    <col min="22" max="22" width="8.109375" style="19" customWidth="1"/>
-    <col min="23" max="23" width="7.5546875" style="19" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.109375" style="19" customWidth="1"/>
-    <col min="25" max="25" width="10.33203125" style="19" customWidth="1"/>
-    <col min="26" max="26" width="7.5546875" style="19" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="10" style="19" customWidth="1"/>
-    <col min="28" max="28" width="8.88671875" style="8"/>
-    <col min="29" max="29" width="8.88671875" style="19"/>
+    <col min="2" max="2" width="20.77734375" style="17" customWidth="1"/>
+    <col min="3" max="3" width="8" style="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="7"/>
+    <col min="6" max="6" width="8.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="23.77734375" style="17" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" style="17" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.77734375" style="17" customWidth="1"/>
+    <col min="11" max="11" width="9.88671875" style="17" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.77734375" style="7" customWidth="1"/>
+    <col min="14" max="14" width="12.88671875" style="44" customWidth="1"/>
+    <col min="15" max="15" width="17.5546875" style="44" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.5546875" style="44" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.109375" style="44" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.77734375" style="44" customWidth="1"/>
+    <col min="19" max="19" width="14.109375" style="44" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21.77734375" style="17" customWidth="1"/>
+    <col min="21" max="21" width="23" style="17" customWidth="1"/>
+    <col min="22" max="22" width="13.6640625" style="17" customWidth="1"/>
+    <col min="23" max="23" width="13.5546875" style="17" customWidth="1"/>
+    <col min="24" max="24" width="17.109375" style="17" customWidth="1"/>
+    <col min="25" max="25" width="10.33203125" style="17" customWidth="1"/>
+    <col min="26" max="26" width="15.109375" style="17" customWidth="1"/>
+    <col min="27" max="27" width="10" style="17" customWidth="1"/>
+    <col min="28" max="28" width="8.88671875" style="7"/>
+    <col min="29" max="29" width="20.6640625" style="17" customWidth="1"/>
     <col min="30" max="30" width="8.88671875" style="5"/>
     <col min="31" max="31" width="9.77734375" style="5" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="11.21875" style="5" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="9.44140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="7.44140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="11.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="7.88671875" style="5" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="9.44140625" style="5" customWidth="1"/>
-    <col min="38" max="38" width="7.44140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="12.6640625" style="5" customWidth="1"/>
-    <col min="40" max="40" width="9.44140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="7.44140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="13.21875" style="5" customWidth="1"/>
-    <col min="43" max="44" width="10.88671875" style="5" customWidth="1"/>
-    <col min="45" max="45" width="8.33203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="4.44140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="47" max="48" width="6.109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="11.21875" style="5" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="10.109375" style="5" customWidth="1"/>
-    <col min="51" max="51" width="10.5546875" style="5" customWidth="1"/>
-    <col min="52" max="52" width="9" style="5" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="9.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.21875" style="16" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="9.44140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="7.44140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="11.6640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="7.88671875" style="16" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="9.44140625" style="16" customWidth="1"/>
+    <col min="38" max="38" width="7.44140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="12.6640625" style="16" customWidth="1"/>
+    <col min="40" max="40" width="9.44140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="7.44140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="13.21875" style="16" customWidth="1"/>
+    <col min="43" max="44" width="10.88671875" style="16" customWidth="1"/>
+    <col min="45" max="45" width="8.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="4.44140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="47" max="48" width="6.109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="11.21875" style="16" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="10.109375" style="16" customWidth="1"/>
+    <col min="51" max="51" width="10.5546875" style="16" customWidth="1"/>
+    <col min="52" max="52" width="9" style="16" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="9.33203125" style="16" bestFit="1" customWidth="1"/>
     <col min="54" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:53" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="1" spans="2:53" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="33"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
+      <c r="AF1" s="34"/>
+      <c r="AG1" s="34"/>
+      <c r="AH1" s="34"/>
+      <c r="AI1" s="34"/>
+      <c r="AJ1" s="34"/>
+      <c r="AK1" s="34"/>
+      <c r="AL1" s="34"/>
+      <c r="AM1" s="34"/>
+      <c r="AN1" s="34"/>
+      <c r="AO1" s="34"/>
+      <c r="AP1" s="34"/>
+      <c r="AQ1" s="34"/>
+      <c r="AR1" s="34"/>
+      <c r="AS1" s="34"/>
+      <c r="AT1" s="34"/>
+      <c r="AU1" s="34"/>
+      <c r="AV1" s="34"/>
+      <c r="AW1" s="34"/>
+      <c r="AX1" s="34"/>
+      <c r="AY1" s="34"/>
+      <c r="AZ1" s="34"/>
+      <c r="BA1" s="34"/>
+    </row>
     <row r="2" spans="2:53" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B2" s="10"/>
+      <c r="B2" s="9"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
-      <c r="R2" s="11"/>
-      <c r="S2" s="11"/>
-      <c r="T2" s="11"/>
-      <c r="U2" s="11"/>
-      <c r="V2" s="11"/>
-      <c r="W2" s="11"/>
-      <c r="X2" s="11"/>
-      <c r="Y2" s="11"/>
-      <c r="Z2" s="11"/>
-      <c r="AA2" s="11"/>
-      <c r="AB2" s="11"/>
-      <c r="AC2" s="11"/>
-      <c r="AF2" s="11"/>
-      <c r="AG2" s="11"/>
-      <c r="AH2" s="11"/>
-      <c r="AI2" s="11"/>
-      <c r="AJ2" s="11"/>
-      <c r="AK2" s="11"/>
-      <c r="AL2" s="11"/>
-      <c r="AM2" s="11"/>
-      <c r="AN2" s="11"/>
-      <c r="AO2" s="11"/>
-      <c r="AP2" s="11"/>
-      <c r="AQ2" s="11"/>
-      <c r="AR2" s="11"/>
-      <c r="AS2" s="11"/>
-      <c r="AT2" s="11"/>
-      <c r="AU2" s="11"/>
-      <c r="AV2" s="11"/>
-      <c r="AW2" s="11"/>
-      <c r="AX2" s="11"/>
-      <c r="AY2" s="11"/>
-      <c r="AZ2" s="11"/>
-      <c r="BA2" s="11"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="10"/>
+      <c r="V2" s="10"/>
+      <c r="W2" s="10"/>
+      <c r="X2" s="10"/>
+      <c r="Y2" s="10"/>
+      <c r="Z2" s="10"/>
+      <c r="AA2" s="10"/>
+      <c r="AB2" s="10"/>
+      <c r="AC2" s="10"/>
+      <c r="AF2" s="35"/>
+      <c r="AG2" s="35"/>
+      <c r="AH2" s="35"/>
+      <c r="AI2" s="35"/>
+      <c r="AJ2" s="35"/>
+      <c r="AK2" s="35"/>
+      <c r="AL2" s="35"/>
+      <c r="AM2" s="35"/>
+      <c r="AN2" s="35"/>
+      <c r="AO2" s="35"/>
+      <c r="AP2" s="35"/>
+      <c r="AQ2" s="35"/>
+      <c r="AR2" s="35"/>
+      <c r="AS2" s="35"/>
+      <c r="AT2" s="35"/>
+      <c r="AU2" s="35"/>
+      <c r="AV2" s="35"/>
+      <c r="AW2" s="35"/>
+      <c r="AX2" s="35"/>
+      <c r="AY2" s="35"/>
+      <c r="AZ2" s="35"/>
+      <c r="BA2" s="35"/>
     </row>
     <row r="3" spans="2:53" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="13"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14"/>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14"/>
-      <c r="V3" s="14"/>
-      <c r="W3" s="14"/>
-      <c r="X3" s="14"/>
-      <c r="Y3" s="14"/>
-      <c r="Z3" s="14"/>
-      <c r="AA3" s="14"/>
-      <c r="AB3" s="14"/>
-      <c r="AC3" s="14"/>
-      <c r="AF3" s="14"/>
-      <c r="AG3" s="14"/>
-      <c r="AH3" s="14"/>
-      <c r="AI3" s="14"/>
-      <c r="AJ3" s="14"/>
-      <c r="AK3" s="14"/>
-      <c r="AL3" s="14"/>
-      <c r="AM3" s="14"/>
-      <c r="AN3" s="14"/>
-      <c r="AO3" s="14"/>
-      <c r="AP3" s="14"/>
-      <c r="AQ3" s="14"/>
-      <c r="AR3" s="14"/>
-      <c r="AS3" s="14"/>
-      <c r="AT3" s="14"/>
-      <c r="AU3" s="14"/>
-      <c r="AV3" s="14"/>
-      <c r="AW3" s="14"/>
-      <c r="AX3" s="14"/>
-      <c r="AY3" s="14"/>
-      <c r="AZ3" s="14"/>
-      <c r="BA3" s="14"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="36"/>
+      <c r="O3" s="36"/>
+      <c r="P3" s="36"/>
+      <c r="Q3" s="36"/>
+      <c r="R3" s="36"/>
+      <c r="S3" s="36"/>
+      <c r="T3" s="13"/>
+      <c r="U3" s="13"/>
+      <c r="V3" s="13"/>
+      <c r="W3" s="13"/>
+      <c r="X3" s="13"/>
+      <c r="Y3" s="13"/>
+      <c r="Z3" s="13"/>
+      <c r="AA3" s="13"/>
+      <c r="AB3" s="13"/>
+      <c r="AC3" s="13"/>
+      <c r="AF3" s="36"/>
+      <c r="AG3" s="36"/>
+      <c r="AH3" s="36"/>
+      <c r="AI3" s="36"/>
+      <c r="AJ3" s="36"/>
+      <c r="AK3" s="36"/>
+      <c r="AL3" s="36"/>
+      <c r="AM3" s="36"/>
+      <c r="AN3" s="36"/>
+      <c r="AO3" s="36"/>
+      <c r="AP3" s="36"/>
+      <c r="AQ3" s="36"/>
+      <c r="AR3" s="36"/>
+      <c r="AS3" s="36"/>
+      <c r="AT3" s="36"/>
+      <c r="AU3" s="36"/>
+      <c r="AV3" s="36"/>
+      <c r="AW3" s="36"/>
+      <c r="AX3" s="36"/>
+      <c r="AY3" s="36"/>
+      <c r="AZ3" s="36"/>
+      <c r="BA3" s="36"/>
     </row>
     <row r="4" spans="2:53" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B4" s="15"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="11"/>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="11"/>
-      <c r="R4" s="11"/>
-      <c r="S4" s="11"/>
-      <c r="T4" s="11"/>
-      <c r="U4" s="11"/>
-      <c r="V4" s="11"/>
-      <c r="W4" s="11"/>
-      <c r="X4" s="11"/>
-      <c r="Y4" s="11"/>
-      <c r="Z4" s="11"/>
-      <c r="AA4" s="11"/>
-      <c r="AB4" s="11"/>
-      <c r="AC4" s="11"/>
-      <c r="AF4" s="11"/>
-      <c r="AG4" s="11"/>
-      <c r="AH4" s="11"/>
-      <c r="AI4" s="11"/>
-      <c r="AJ4" s="11"/>
-      <c r="AK4" s="11"/>
-      <c r="AL4" s="11"/>
-      <c r="AM4" s="11"/>
-      <c r="AN4" s="11"/>
-      <c r="AO4" s="11"/>
-      <c r="AP4" s="11"/>
-      <c r="AQ4" s="11"/>
-      <c r="AR4" s="11"/>
-      <c r="AS4" s="11"/>
-      <c r="AT4" s="11"/>
-      <c r="AU4" s="11"/>
-      <c r="AV4" s="11"/>
-      <c r="AW4" s="11"/>
-      <c r="AX4" s="11"/>
-      <c r="AY4" s="11"/>
-      <c r="AZ4" s="11"/>
-      <c r="BA4" s="11"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="35"/>
+      <c r="O4" s="35"/>
+      <c r="P4" s="35"/>
+      <c r="Q4" s="35"/>
+      <c r="R4" s="35"/>
+      <c r="S4" s="35"/>
+      <c r="T4" s="10"/>
+      <c r="U4" s="10"/>
+      <c r="V4" s="10"/>
+      <c r="W4" s="10"/>
+      <c r="X4" s="10"/>
+      <c r="Y4" s="10"/>
+      <c r="Z4" s="10"/>
+      <c r="AA4" s="10"/>
+      <c r="AB4" s="10"/>
+      <c r="AC4" s="10"/>
+      <c r="AF4" s="35"/>
+      <c r="AG4" s="35"/>
+      <c r="AH4" s="35"/>
+      <c r="AI4" s="35"/>
+      <c r="AJ4" s="35"/>
+      <c r="AK4" s="35"/>
+      <c r="AL4" s="35"/>
+      <c r="AM4" s="35"/>
+      <c r="AN4" s="35"/>
+      <c r="AO4" s="35"/>
+      <c r="AP4" s="35"/>
+      <c r="AQ4" s="35"/>
+      <c r="AR4" s="35"/>
+      <c r="AS4" s="35"/>
+      <c r="AT4" s="35"/>
+      <c r="AU4" s="35"/>
+      <c r="AV4" s="35"/>
+      <c r="AW4" s="35"/>
+      <c r="AX4" s="35"/>
+      <c r="AY4" s="35"/>
+      <c r="AZ4" s="35"/>
+      <c r="BA4" s="35"/>
     </row>
     <row r="5" spans="2:53" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B5" s="15"/>
-      <c r="C5" s="11"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="10"/>
+      <c r="N5" s="37"/>
+      <c r="O5" s="37"/>
+      <c r="P5" s="37"/>
+      <c r="Q5" s="37"/>
+      <c r="R5" s="37"/>
+      <c r="S5" s="37"/>
+      <c r="AF5" s="37"/>
+      <c r="AG5" s="37"/>
+      <c r="AH5" s="37"/>
+      <c r="AI5" s="37"/>
+      <c r="AJ5" s="37"/>
+      <c r="AK5" s="37"/>
+      <c r="AL5" s="37"/>
+      <c r="AM5" s="37"/>
+      <c r="AN5" s="37"/>
+      <c r="AO5" s="37"/>
+      <c r="AP5" s="37"/>
+      <c r="AQ5" s="37"/>
+      <c r="AR5" s="37"/>
+      <c r="AS5" s="37"/>
+      <c r="AT5" s="37"/>
+      <c r="AU5" s="37"/>
+      <c r="AV5" s="37"/>
+      <c r="AW5" s="37"/>
+      <c r="AX5" s="37"/>
+      <c r="AY5" s="37"/>
+      <c r="AZ5" s="37"/>
+      <c r="BA5" s="37"/>
     </row>
     <row r="6" spans="2:53" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="C6" s="20"/>
-      <c r="D6" s="7"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="6"/>
+      <c r="N6" s="37"/>
+      <c r="O6" s="37"/>
+      <c r="P6" s="37"/>
+      <c r="Q6" s="37"/>
+      <c r="R6" s="37"/>
+      <c r="S6" s="37"/>
+      <c r="AF6" s="37"/>
+      <c r="AG6" s="37"/>
+      <c r="AH6" s="37"/>
+      <c r="AI6" s="37"/>
+      <c r="AJ6" s="37"/>
+      <c r="AK6" s="37"/>
+      <c r="AL6" s="37"/>
+      <c r="AM6" s="37"/>
+      <c r="AN6" s="37"/>
+      <c r="AO6" s="37"/>
+      <c r="AP6" s="37"/>
+      <c r="AQ6" s="37"/>
+      <c r="AR6" s="37"/>
+      <c r="AS6" s="37"/>
+      <c r="AT6" s="37"/>
+      <c r="AU6" s="37"/>
+      <c r="AV6" s="37"/>
+      <c r="AW6" s="37"/>
+      <c r="AX6" s="37"/>
+      <c r="AY6" s="37"/>
+      <c r="AZ6" s="37"/>
+      <c r="BA6" s="37"/>
     </row>
     <row r="7" spans="2:53" s="3" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="16"/>
+      <c r="B7" s="15"/>
+      <c r="N7" s="37"/>
+      <c r="O7" s="37"/>
+      <c r="P7" s="37"/>
+      <c r="Q7" s="37"/>
+      <c r="R7" s="37"/>
+      <c r="S7" s="37"/>
+      <c r="AF7" s="37"/>
+      <c r="AG7" s="37"/>
+      <c r="AH7" s="37"/>
+      <c r="AI7" s="37"/>
+      <c r="AJ7" s="37"/>
+      <c r="AK7" s="37"/>
+      <c r="AL7" s="37"/>
+      <c r="AM7" s="37"/>
+      <c r="AN7" s="37"/>
+      <c r="AO7" s="37"/>
+      <c r="AP7" s="37"/>
+      <c r="AQ7" s="37"/>
+      <c r="AR7" s="37"/>
+      <c r="AS7" s="37"/>
+      <c r="AT7" s="37"/>
+      <c r="AU7" s="37"/>
+      <c r="AV7" s="37"/>
+      <c r="AW7" s="37"/>
+      <c r="AX7" s="37"/>
+      <c r="AY7" s="37"/>
+      <c r="AZ7" s="37"/>
+      <c r="BA7" s="37"/>
     </row>
     <row r="8" spans="2:53" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F8" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="21" t="s">
+      <c r="G8" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="H8" s="21" t="s">
+      <c r="H8" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="I8" s="21" t="s">
+      <c r="I8" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J8" s="21" t="s">
+      <c r="J8" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="K8" s="21" t="s">
+      <c r="K8" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="L8" s="21" t="s">
+      <c r="L8" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="M8" s="21" t="s">
+      <c r="M8" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="N8" s="21" t="s">
+      <c r="N8" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="O8" s="27" t="s">
+      <c r="O8" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="P8" s="27" t="s">
+      <c r="P8" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="Q8" s="21" t="s">
+      <c r="Q8" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="R8" s="21" t="s">
+      <c r="R8" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="S8" s="21" t="s">
+      <c r="S8" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="T8" s="21" t="s">
+      <c r="T8" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="U8" s="21"/>
-      <c r="V8" s="21" t="s">
+      <c r="U8" s="20"/>
+      <c r="V8" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="W8" s="21"/>
-      <c r="X8" s="21" t="s">
+      <c r="W8" s="20"/>
+      <c r="X8" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="Y8" s="21"/>
-      <c r="Z8" s="21"/>
-      <c r="AA8" s="21"/>
-      <c r="AB8" s="21" t="s">
+      <c r="Y8" s="20"/>
+      <c r="Z8" s="20"/>
+      <c r="AA8" s="20"/>
+      <c r="AB8" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AC8" s="34" t="s">
+      <c r="AC8" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="AD8" s="8"/>
-      <c r="AE8" s="8"/>
-      <c r="AF8" s="24" t="s">
+      <c r="AD8" s="7"/>
+      <c r="AE8" s="7"/>
+      <c r="AF8" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="AG8" s="21"/>
-      <c r="AH8" s="21"/>
-      <c r="AI8" s="21"/>
-      <c r="AJ8" s="21"/>
-      <c r="AK8" s="21"/>
-      <c r="AL8" s="21"/>
-      <c r="AM8" s="21"/>
-      <c r="AN8" s="21"/>
-      <c r="AO8" s="21"/>
-      <c r="AP8" s="21"/>
-      <c r="AQ8" s="21"/>
-      <c r="AR8" s="21"/>
-      <c r="AS8" s="21"/>
-      <c r="AT8" s="21"/>
-      <c r="AU8" s="21"/>
-      <c r="AV8" s="21"/>
-      <c r="AW8" s="21"/>
-      <c r="AX8" s="21"/>
-      <c r="AY8" s="21"/>
-      <c r="AZ8" s="21"/>
-      <c r="BA8" s="34"/>
+      <c r="AG8" s="38"/>
+      <c r="AH8" s="38"/>
+      <c r="AI8" s="38"/>
+      <c r="AJ8" s="38"/>
+      <c r="AK8" s="38"/>
+      <c r="AL8" s="38"/>
+      <c r="AM8" s="38"/>
+      <c r="AN8" s="38"/>
+      <c r="AO8" s="38"/>
+      <c r="AP8" s="38"/>
+      <c r="AQ8" s="38"/>
+      <c r="AR8" s="38"/>
+      <c r="AS8" s="38"/>
+      <c r="AT8" s="38"/>
+      <c r="AU8" s="38"/>
+      <c r="AV8" s="38"/>
+      <c r="AW8" s="38"/>
+      <c r="AX8" s="38"/>
+      <c r="AY8" s="38"/>
+      <c r="AZ8" s="38"/>
+      <c r="BA8" s="46"/>
     </row>
     <row r="9" spans="2:53" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="25"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
       <c r="F9" s="22"/>
       <c r="G9" s="22"/>
       <c r="H9" s="22"/>
       <c r="I9" s="22"/>
-      <c r="J9" s="30"/>
+      <c r="J9" s="26"/>
       <c r="K9" s="22"/>
       <c r="L9" s="22"/>
-      <c r="M9" s="30"/>
-      <c r="N9" s="22"/>
-      <c r="O9" s="28"/>
-      <c r="P9" s="28"/>
-      <c r="Q9" s="22"/>
-      <c r="R9" s="22"/>
-      <c r="S9" s="22"/>
+      <c r="M9" s="26"/>
+      <c r="N9" s="40"/>
+      <c r="O9" s="41"/>
+      <c r="P9" s="41"/>
+      <c r="Q9" s="40"/>
+      <c r="R9" s="40"/>
+      <c r="S9" s="40"/>
       <c r="T9" s="22" t="s">
         <v>15</v>
       </c>
@@ -1465,83 +1615,83 @@
       </c>
       <c r="AA9" s="22"/>
       <c r="AB9" s="22"/>
-      <c r="AC9" s="35"/>
-      <c r="AD9" s="8"/>
-      <c r="AE9" s="8"/>
-      <c r="AF9" s="37" t="s">
+      <c r="AC9" s="24"/>
+      <c r="AD9" s="7"/>
+      <c r="AE9" s="7"/>
+      <c r="AF9" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="AG9" s="32"/>
-      <c r="AH9" s="32"/>
-      <c r="AI9" s="32"/>
-      <c r="AJ9" s="32" t="s">
+      <c r="AG9" s="48"/>
+      <c r="AH9" s="48"/>
+      <c r="AI9" s="48"/>
+      <c r="AJ9" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="AK9" s="32"/>
-      <c r="AL9" s="32"/>
-      <c r="AM9" s="32"/>
-      <c r="AN9" s="32" t="s">
+      <c r="AK9" s="48"/>
+      <c r="AL9" s="48"/>
+      <c r="AM9" s="48"/>
+      <c r="AN9" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="AO9" s="32" t="s">
+      <c r="AO9" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="AP9" s="32" t="s">
+      <c r="AP9" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="AQ9" s="32" t="s">
+      <c r="AQ9" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="AR9" s="32" t="s">
+      <c r="AR9" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="AS9" s="32" t="s">
+      <c r="AS9" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="AT9" s="32" t="s">
+      <c r="AT9" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="AU9" s="32" t="s">
+      <c r="AU9" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="AV9" s="32" t="s">
+      <c r="AV9" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="AW9" s="32" t="s">
+      <c r="AW9" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="AX9" s="32" t="s">
+      <c r="AX9" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="AY9" s="32" t="s">
+      <c r="AY9" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="AZ9" s="32" t="s">
+      <c r="AZ9" s="48" t="s">
         <v>31</v>
       </c>
-      <c r="BA9" s="38" t="s">
+      <c r="BA9" s="49" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="2:53" s="2" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="26"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
+    <row r="10" spans="2:53" s="2" customFormat="1" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="32"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
       <c r="F10" s="23"/>
       <c r="G10" s="23"/>
       <c r="H10" s="23"/>
       <c r="I10" s="23"/>
-      <c r="J10" s="31"/>
+      <c r="J10" s="27"/>
       <c r="K10" s="23"/>
       <c r="L10" s="23"/>
-      <c r="M10" s="31"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="29"/>
-      <c r="P10" s="29"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="23"/>
-      <c r="S10" s="23"/>
+      <c r="M10" s="27"/>
+      <c r="N10" s="42"/>
+      <c r="O10" s="43"/>
+      <c r="P10" s="43"/>
+      <c r="Q10" s="42"/>
+      <c r="R10" s="42"/>
+      <c r="S10" s="42"/>
       <c r="T10" s="23"/>
       <c r="U10" s="23"/>
       <c r="V10" s="23"/>
@@ -1559,56 +1709,86 @@
         <v>21</v>
       </c>
       <c r="AB10" s="23"/>
-      <c r="AC10" s="36"/>
-      <c r="AD10" s="8"/>
-      <c r="AE10" s="8"/>
-      <c r="AF10" s="17" t="s">
+      <c r="AC10" s="25"/>
+      <c r="AD10" s="7"/>
+      <c r="AE10" s="7"/>
+      <c r="AF10" s="50" t="s">
         <v>48</v>
       </c>
-      <c r="AG10" s="6" t="s">
+      <c r="AG10" s="51" t="s">
         <v>49</v>
       </c>
-      <c r="AH10" s="6" t="s">
+      <c r="AH10" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="AI10" s="6" t="s">
+      <c r="AI10" s="51" t="s">
         <v>51</v>
       </c>
-      <c r="AJ10" s="6" t="s">
+      <c r="AJ10" s="51" t="s">
         <v>48</v>
       </c>
-      <c r="AK10" s="6" t="s">
+      <c r="AK10" s="51" t="s">
         <v>49</v>
       </c>
-      <c r="AL10" s="6" t="s">
+      <c r="AL10" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="AM10" s="6" t="s">
+      <c r="AM10" s="51" t="s">
         <v>51</v>
       </c>
-      <c r="AN10" s="33"/>
-      <c r="AO10" s="33"/>
-      <c r="AP10" s="33"/>
-      <c r="AQ10" s="33"/>
-      <c r="AR10" s="33"/>
-      <c r="AS10" s="33"/>
-      <c r="AT10" s="33"/>
-      <c r="AU10" s="33"/>
-      <c r="AV10" s="33"/>
-      <c r="AW10" s="33"/>
-      <c r="AX10" s="33"/>
-      <c r="AY10" s="33"/>
-      <c r="AZ10" s="33"/>
-      <c r="BA10" s="39"/>
+      <c r="AN10" s="52"/>
+      <c r="AO10" s="52"/>
+      <c r="AP10" s="52"/>
+      <c r="AQ10" s="52"/>
+      <c r="AR10" s="52"/>
+      <c r="AS10" s="52"/>
+      <c r="AT10" s="52"/>
+      <c r="AU10" s="52"/>
+      <c r="AV10" s="52"/>
+      <c r="AW10" s="52"/>
+      <c r="AX10" s="52"/>
+      <c r="AY10" s="52"/>
+      <c r="AZ10" s="52"/>
+      <c r="BA10" s="53"/>
     </row>
     <row r="11" spans="2:53" x14ac:dyDescent="0.3">
-      <c r="BA11" s="18">
+      <c r="BA11" s="16">
         <f>SUM(AF11:AZ11)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="46">
+    <mergeCell ref="G8:G10"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="S8:S10"/>
+    <mergeCell ref="H8:H10"/>
+    <mergeCell ref="I8:I10"/>
+    <mergeCell ref="J8:J10"/>
+    <mergeCell ref="K8:K10"/>
+    <mergeCell ref="L8:L10"/>
+    <mergeCell ref="M8:M10"/>
+    <mergeCell ref="N8:N10"/>
+    <mergeCell ref="O8:O10"/>
+    <mergeCell ref="P8:P10"/>
+    <mergeCell ref="Q8:Q10"/>
+    <mergeCell ref="R8:R10"/>
+    <mergeCell ref="AX9:AX10"/>
+    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="V8:W8"/>
+    <mergeCell ref="X8:AA8"/>
+    <mergeCell ref="AB8:AB10"/>
+    <mergeCell ref="AC8:AC10"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="U9:U10"/>
+    <mergeCell ref="V9:V10"/>
+    <mergeCell ref="W9:W10"/>
+    <mergeCell ref="X9:Y9"/>
+    <mergeCell ref="Z9:AA9"/>
     <mergeCell ref="AY9:AY10"/>
     <mergeCell ref="AF8:BA8"/>
     <mergeCell ref="AF9:AI9"/>
@@ -1625,57 +1805,12 @@
     <mergeCell ref="AU9:AU10"/>
     <mergeCell ref="AV9:AV10"/>
     <mergeCell ref="AW9:AW10"/>
-    <mergeCell ref="AX9:AX10"/>
-    <mergeCell ref="T8:U8"/>
-    <mergeCell ref="V8:W8"/>
-    <mergeCell ref="X8:AA8"/>
-    <mergeCell ref="AB8:AB10"/>
-    <mergeCell ref="AC8:AC10"/>
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="V9:V10"/>
-    <mergeCell ref="W9:W10"/>
-    <mergeCell ref="X9:Y9"/>
-    <mergeCell ref="Z9:AA9"/>
-    <mergeCell ref="S8:S10"/>
-    <mergeCell ref="H8:H10"/>
-    <mergeCell ref="I8:I10"/>
-    <mergeCell ref="J8:J10"/>
-    <mergeCell ref="K8:K10"/>
-    <mergeCell ref="L8:L10"/>
-    <mergeCell ref="M8:M10"/>
-    <mergeCell ref="N8:N10"/>
-    <mergeCell ref="O8:O10"/>
-    <mergeCell ref="P8:P10"/>
-    <mergeCell ref="Q8:Q10"/>
-    <mergeCell ref="R8:R10"/>
-    <mergeCell ref="G8:G10"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="F8:F10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DFE98289BC91294F829EFFD4DC549C76" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="19972903a613892b44bc7de177b9930c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="24f70235-d7ab-48ae-872a-f5e45d821dca" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="851bba6bbcd0ff4aaccc95eb8de2c74d" ns3:_="">
     <xsd:import namespace="24f70235-d7ab-48ae-872a-f5e45d821dca"/>
@@ -1825,31 +1960,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D6BA337-C593-4EF2-B090-937D907018AE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="24f70235-d7ab-48ae-872a-f5e45d821dca"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{961ECCB7-21B8-4C05-838A-3ADAC8FDED02}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E727EF53-D248-4693-8734-5FECE57054A9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1865,4 +1991,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{961ECCB7-21B8-4C05-838A-3ADAC8FDED02}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D6BA337-C593-4EF2-B090-937D907018AE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="24f70235-d7ab-48ae-872a-f5e45d821dca"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>